--- a/data/trans_orig/AIRE_1_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1_R-Edad-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19603</t>
+          <t>19909</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26653</t>
+          <t>26717</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14440</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20891</t>
+          <t>20722</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36406</t>
+          <t>36498</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46361</t>
+          <t>45740</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>81,46%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10344</t>
+          <t>10038</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5486</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11768</t>
+          <t>12208</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9793</t>
+          <t>10414</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19748</t>
+          <t>19656</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,0%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50897</t>
+          <t>52047</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62696</t>
+          <t>63052</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66635</t>
+          <t>66534</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81952</t>
+          <t>80769</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>122660</t>
+          <t>122802</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>140178</t>
+          <t>140735</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,62%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11878</t>
+          <t>11522</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23677</t>
+          <t>22527</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15893</t>
+          <t>17076</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31210</t>
+          <t>31311</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32241</t>
+          <t>31684</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>49759</t>
+          <t>49617</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48234</t>
+          <t>48071</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63973</t>
+          <t>63113</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72151</t>
+          <t>72915</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91963</t>
+          <t>91462</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>126089</t>
+          <t>125564</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>151243</t>
+          <t>150385</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,37%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20347</t>
+          <t>21207</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36086</t>
+          <t>36249</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25918</t>
+          <t>26419</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45730</t>
+          <t>44966</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>50957</t>
+          <t>51815</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>76111</t>
+          <t>76636</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,9%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>105050</t>
+          <t>105396</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128146</t>
+          <t>128766</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>93595</t>
+          <t>92909</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>116479</t>
+          <t>116046</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>205136</t>
+          <t>206010</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>242317</t>
+          <t>243005</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,7%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14556</t>
+          <t>13936</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37652</t>
+          <t>37306</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27737</t>
+          <t>28170</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50621</t>
+          <t>51307</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44601</t>
+          <t>43913</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>81782</t>
+          <t>80908</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,2%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>237616</t>
+          <t>239906</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>272868</t>
+          <t>273005</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>261692</t>
+          <t>262850</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>296993</t>
+          <t>297538</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>511856</t>
+          <t>510709</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>561089</t>
+          <t>560991</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,17%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>58675</t>
+          <t>58538</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93927</t>
+          <t>91637</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89156</t>
+          <t>88611</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>124457</t>
+          <t>123299</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>156602</t>
+          <t>156700</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>205835</t>
+          <t>206982</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/AIRE_1_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1_R-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13964</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10994</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16675</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>66,63%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>52,46%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>79,57%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>23780</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19909</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>26717</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>79,41%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>66,48%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>89,21%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17843</t>
+          <t>21410</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>17796</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20722</t>
+          <t>24239</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>41623</t>
+          <t>35374</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36498</t>
+          <t>31280</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45740</t>
+          <t>38906</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>80,98%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6992</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4281</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9962</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>33,37%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>20,43%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>47,54%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>6167</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3230</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10038</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>20,59%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>10,79%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>33,52%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8365</t>
+          <t>5675</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5486</t>
+          <t>2846</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12208</t>
+          <t>9289</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>14531</t>
+          <t>12667</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10414</t>
+          <t>9135</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19656</t>
+          <t>16761</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,89%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20956</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20956</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20956</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>29947</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>29947</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>29947</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26208</t>
+          <t>27085</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26208</t>
+          <t>27085</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26208</t>
+          <t>27085</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>56154</t>
+          <t>48041</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>56154</t>
+          <t>48041</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>56154</t>
+          <t>48041</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>64630</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>57724</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>70074</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>76,59%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>68,4%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>83,04%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>57523</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>52047</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>63052</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>77,14%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>69,79%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>84,55%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>74581</t>
+          <t>51143</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66534</t>
+          <t>45720</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80769</t>
+          <t>56358</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>132104</t>
+          <t>115773</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>122802</t>
+          <t>106647</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>140735</t>
+          <t>123690</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,33%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19760</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14316</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>26666</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>23,41%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>16,96%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>31,6%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>17051</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>11522</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>22527</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>22,86%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>15,45%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>30,21%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>23264</t>
+          <t>16557</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17076</t>
+          <t>11342</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31311</t>
+          <t>21980</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>40315</t>
+          <t>36316</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31684</t>
+          <t>28399</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>49617</t>
+          <t>45442</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>29,88%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>84390</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>84390</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>84390</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>74574</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>74574</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>74574</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>97845</t>
+          <t>67700</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>97845</t>
+          <t>67700</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>97845</t>
+          <t>67700</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>172419</t>
+          <t>152089</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>172419</t>
+          <t>152089</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>172419</t>
+          <t>152089</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>79364</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>69969</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>88781</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>70,15%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>61,85%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>78,48%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>56431</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>48071</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>63113</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>66,92%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>57,01%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>74,85%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>82506</t>
+          <t>55703</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72915</t>
+          <t>48060</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91462</t>
+          <t>62615</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>138936</t>
+          <t>135067</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>125564</t>
+          <t>124000</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>150385</t>
+          <t>146585</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,28%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27889</t>
+          <t>33768</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21207</t>
+          <t>24351</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36249</t>
+          <t>43163</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>35375</t>
+          <t>28510</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26419</t>
+          <t>21598</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44966</t>
+          <t>36153</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>63264</t>
+          <t>62279</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>51815</t>
+          <t>50761</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>76636</t>
+          <t>73346</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,17%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>113132</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>113132</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>113132</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>84320</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>84320</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>84320</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>117881</t>
+          <t>84213</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>117881</t>
+          <t>84213</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>117881</t>
+          <t>84213</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>202200</t>
+          <t>197346</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>202200</t>
+          <t>197346</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>202200</t>
+          <t>197346</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>115941</t>
+          <t>102781</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>105396</t>
+          <t>89630</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128766</t>
+          <t>112087</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>106760</t>
+          <t>93440</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>92909</t>
+          <t>85310</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>116046</t>
+          <t>101047</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>222701</t>
+          <t>196221</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>206010</t>
+          <t>181721</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>243005</t>
+          <t>208671</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>79,87%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>36705</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>27399</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>49856</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>26,31%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>19,64%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>35,74%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>26761</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>13936</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>37306</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>18,75%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9,77%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>26,14%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>37456</t>
+          <t>28331</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28170</t>
+          <t>20724</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51307</t>
+          <t>36461</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>64217</t>
+          <t>65036</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43913</t>
+          <t>52586</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>80908</t>
+          <t>79536</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>30,44%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>139486</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>139486</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>139486</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>142702</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>142702</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>142702</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>144216</t>
+          <t>121771</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>144216</t>
+          <t>121771</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>144216</t>
+          <t>121771</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>286918</t>
+          <t>261257</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>286918</t>
+          <t>261257</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>286918</t>
+          <t>261257</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>260739</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>244156</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>275967</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>72,84%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>68,21%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>77,09%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>346</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>253675</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>239906</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>273005</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>76,51%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>72,36%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>82,34%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>281689</t>
+          <t>221696</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>262850</t>
+          <t>208646</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>297538</t>
+          <t>233782</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>535363</t>
+          <t>482435</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>510709</t>
+          <t>461960</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>560991</t>
+          <t>501963</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>76,2%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>97226</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>81998</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>113809</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>27,16%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>22,91%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>31,79%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>77868</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>58538</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>91637</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>23,49%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>17,66%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>27,64%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>104460</t>
+          <t>79073</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>88611</t>
+          <t>66987</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>123299</t>
+          <t>92123</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>182328</t>
+          <t>176298</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>156700</t>
+          <t>156770</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>206982</t>
+          <t>196773</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,87%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>468</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>386149</t>
+          <t>300769</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>386149</t>
+          <t>300769</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>386149</t>
+          <t>300769</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
